--- a/verification/cases/roundtrip/lbo_model/init.xlsx
+++ b/verification/cases/roundtrip/lbo_model/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordilorido/Downloads/LBO 60min/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EC2ED4-8440-8740-B688-5CBE234F728F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D85450F8-B5E2-46C2-94D3-2A5D1B34788A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="-21060" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LBO-60-Minutes" sheetId="1" r:id="rId1"/>
@@ -1665,29 +1665,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="B2:N248"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="3" customWidth="1"/>
     <col min="5" max="8" width="12.6640625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="9" max="13" width="12.6640625" style="3" customWidth="1"/>
     <col min="14" max="14" width="2.6640625" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.1640625" style="3"/>
+    <col min="15" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="155" t="str">
         <f>Company_Name&amp;" - LBO Case Study Model Test"</f>
         <v>Diana Shipping Inc. - LBO Case Study Model Test</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="90" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
@@ -1703,8 +1703,8 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C8" s="90" t="s">
         <v>71</v>
       </c>
@@ -1736,13 +1736,13 @@
       </c>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C9" s="90"/>
       <c r="D9" s="90"/>
       <c r="H9" s="83"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C10" s="90" t="s">
         <v>91</v>
       </c>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C11" s="93" t="s">
         <v>92</v>
       </c>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L11" s="12"/>
     </row>
-    <row r="12" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C12" s="90" t="s">
         <v>93</v>
       </c>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C13" s="102" t="s">
         <v>125</v>
       </c>
@@ -1809,10 +1809,10 @@
       </c>
       <c r="L13" s="12"/>
     </row>
-    <row r="14" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C16" s="90" t="s">
         <v>38</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="17" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="H17" s="102" t="s">
         <v>143</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C18" s="102" t="s">
         <v>130</v>
       </c>
@@ -1856,7 +1856,7 @@
       <c r="J18" s="102"/>
       <c r="K18" s="102"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1872,8 @@
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C22" s="9" t="s">
         <v>28</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C23" s="103" t="s">
         <v>13</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>7.9427262513098906</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C24" s="103" t="s">
         <v>122</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>20.432651448860007</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C25" s="103" t="s">
         <v>123</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>0.40865302897720013</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C26" s="11" t="s">
         <v>20</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>0.33552529165992045</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C27" s="103" t="s">
         <v>132</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>29.119556020807018</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>36</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0.72675464230034148</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C29" s="38" t="s">
         <v>10</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
         <v>146</v>
       </c>
@@ -2085,8 +2085,8 @@
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="D33" s="36" t="s">
         <v>15</v>
@@ -2106,7 +2106,7 @@
       <c r="I33" s="36"/>
       <c r="J33" s="133"/>
     </row>
-    <row r="34" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C34" s="9" t="s">
         <v>147</v>
       </c>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="J34" s="133"/>
     </row>
-    <row r="35" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C35" s="11" t="str">
         <f>+$C$23</f>
         <v>Revolver:</v>
@@ -2146,7 +2146,7 @@
       <c r="I35" s="137"/>
       <c r="J35" s="135"/>
     </row>
-    <row r="36" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C36" s="11" t="str">
         <f>+$C$24</f>
         <v>Term Loans:</v>
@@ -2164,7 +2164,7 @@
       <c r="I36" s="135"/>
       <c r="J36" s="135"/>
     </row>
-    <row r="37" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C37" s="11" t="str">
         <f>+$C$25</f>
         <v>Subordinated Notes:</v>
@@ -2178,7 +2178,7 @@
       <c r="I37" s="138"/>
       <c r="J37" s="135"/>
     </row>
-    <row r="38" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C38" s="11" t="str">
         <f>+$C$26</f>
         <v>Mezzanine:</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="134"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C39" s="103" t="s">
         <v>121</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="17"/>
       <c r="C41" s="18"/>
       <c r="D41" s="19"/>
@@ -2220,7 +2220,7 @@
       <c r="L41" s="21"/>
       <c r="M41" s="21"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="41" t="s">
         <v>41</v>
       </c>
@@ -2265,8 +2265,8 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="43" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="102" t="s">
         <v>98</v>
       </c>
@@ -2295,8 +2295,8 @@
       <c r="L44" s="104"/>
       <c r="M44" s="104"/>
     </row>
-    <row r="45" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C46" s="90" t="s">
         <v>83</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="L46" s="47"/>
       <c r="M46" s="47"/>
     </row>
-    <row r="47" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C47" s="90" t="s">
         <v>85</v>
       </c>
@@ -2346,13 +2346,13 @@
       <c r="L47" s="145"/>
       <c r="M47" s="145"/>
     </row>
-    <row r="48" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
       <c r="G48" s="71"/>
       <c r="I48" s="71"/>
     </row>
-    <row r="49" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C49" s="90" t="s">
         <v>86</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="L49" s="104"/>
       <c r="M49" s="104"/>
     </row>
-    <row r="50" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C50" s="90" t="s">
         <v>87</v>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
     </row>
-    <row r="51" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C51" s="103" t="s">
         <v>116</v>
       </c>
@@ -2431,10 +2431,10 @@
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
     </row>
-    <row r="52" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C52" s="90"/>
     </row>
-    <row r="53" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C53" s="90" t="s">
         <v>89</v>
       </c>
@@ -2459,7 +2459,7 @@
       <c r="L53" s="110"/>
       <c r="M53" s="110"/>
     </row>
-    <row r="54" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C54" s="103" t="s">
         <v>115</v>
       </c>
@@ -2488,11 +2488,11 @@
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
     </row>
-    <row r="55" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C56" s="102" t="s">
         <v>99</v>
       </c>
@@ -2521,7 +2521,7 @@
       <c r="L56" s="109"/>
       <c r="M56" s="109"/>
     </row>
-    <row r="57" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C57" s="103" t="s">
         <v>115</v>
       </c>
@@ -2546,7 +2546,7 @@
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
     </row>
-    <row r="58" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C58" s="11" t="s">
         <v>42</v>
       </c>
@@ -2575,8 +2575,8 @@
       <c r="L58" s="72"/>
       <c r="M58" s="72"/>
     </row>
-    <row r="59" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C60" s="102" t="s">
         <v>117</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="L60" s="111"/>
       <c r="M60" s="111"/>
     </row>
-    <row r="61" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C61" s="103" t="s">
         <v>115</v>
       </c>
@@ -2630,8 +2630,8 @@
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
     </row>
-    <row r="62" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="102" t="s">
         <v>118</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="L63" s="71"/>
       <c r="M63" s="71"/>
     </row>
-    <row r="64" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="103" t="s">
         <v>115</v>
       </c>
@@ -2685,8 +2685,8 @@
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
     </row>
-    <row r="65" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="66" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="102" t="s">
         <v>119</v>
       </c>
@@ -2715,7 +2715,7 @@
       <c r="L66" s="71"/>
       <c r="M66" s="71"/>
     </row>
-    <row r="67" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="103" t="s">
         <v>115</v>
       </c>
@@ -2740,10 +2740,10 @@
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
     </row>
-    <row r="68" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C68" s="102"/>
     </row>
-    <row r="69" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="102" t="s">
         <v>120</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="L69" s="13"/>
       <c r="M69" s="13"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="17"/>
       <c r="C71" s="18"/>
       <c r="D71" s="19"/>
@@ -2790,7 +2790,7 @@
       <c r="L71" s="21"/>
       <c r="M71" s="21"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="41" t="s">
         <v>70</v>
       </c>
@@ -2836,10 +2836,10 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="73" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="H73" s="151"/>
     </row>
-    <row r="74" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="103" t="s">
         <v>75</v>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="L74" s="112"/>
       <c r="M74" s="112"/>
     </row>
-    <row r="75" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="95" t="s">
         <v>76</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="L75" s="47"/>
       <c r="M75" s="47"/>
     </row>
-    <row r="76" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="43" t="s">
         <v>77</v>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="L76" s="46"/>
       <c r="M76" s="46"/>
     </row>
-    <row r="77" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="26" t="s">
         <v>149</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>5.7894871893563238E-2</v>
       </c>
       <c r="G77" s="128">
-        <f t="shared" ref="G77:I77" si="7">+G76/F76-1</f>
+        <f t="shared" ref="G77:H77" si="7">+G76/F76-1</f>
         <v>-0.1378137298300296</v>
       </c>
       <c r="H77" s="128">
@@ -2946,8 +2946,8 @@
       <c r="L77" s="128"/>
       <c r="M77" s="128"/>
     </row>
-    <row r="78" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C79" s="90" t="s">
         <v>82</v>
       </c>
@@ -2972,8 +2972,8 @@
       <c r="L79" s="47"/>
       <c r="M79" s="47"/>
     </row>
-    <row r="80" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="81" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C81" s="93" t="s">
         <v>78</v>
       </c>
@@ -2998,7 +2998,7 @@
       <c r="L81" s="47"/>
       <c r="M81" s="47"/>
     </row>
-    <row r="82" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C82" s="93" t="s">
         <v>6</v>
       </c>
@@ -3023,7 +3023,7 @@
       <c r="L82" s="47"/>
       <c r="M82" s="47"/>
     </row>
-    <row r="83" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C83" s="93" t="s">
         <v>79</v>
       </c>
@@ -3048,7 +3048,7 @@
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
     </row>
-    <row r="84" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C84" s="93" t="s">
         <v>80</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
     </row>
-    <row r="85" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C85" s="43" t="s">
         <v>81</v>
       </c>
@@ -3103,8 +3103,8 @@
       <c r="L85" s="46"/>
       <c r="M85" s="46"/>
     </row>
-    <row r="86" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="87" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C87" s="4" t="s">
         <v>97</v>
       </c>
@@ -3133,12 +3133,12 @@
       <c r="L87" s="51"/>
       <c r="M87" s="51"/>
     </row>
-    <row r="88" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C88" s="90"/>
       <c r="F88" s="132"/>
       <c r="G88" s="132"/>
     </row>
-    <row r="89" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C89" s="103" t="s">
         <v>94</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="L89" s="12"/>
       <c r="M89" s="12"/>
     </row>
-    <row r="90" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C90" s="103" t="s">
         <v>95</v>
       </c>
@@ -3188,7 +3188,7 @@
       <c r="L90" s="12"/>
       <c r="M90" s="12"/>
     </row>
-    <row r="91" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C91" s="43" t="s">
         <v>145</v>
       </c>
@@ -3217,8 +3217,8 @@
       <c r="L91" s="46"/>
       <c r="M91" s="46"/>
     </row>
-    <row r="92" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C93" s="4" t="s">
         <v>96</v>
       </c>
@@ -3247,7 +3247,7 @@
       <c r="L93" s="51"/>
       <c r="M93" s="51"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C94" s="26"/>
       <c r="F94" s="12"/>
       <c r="G94" s="12"/>
@@ -3258,7 +3258,7 @@
       <c r="L94" s="12"/>
       <c r="M94" s="12"/>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="31"/>
       <c r="C95" s="32"/>
       <c r="D95" s="33"/>
@@ -3278,7 +3278,7 @@
       <c r="L95" s="21"/>
       <c r="M95" s="21"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96" s="5" t="s">
         <v>100</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="97" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C97" s="26"/>
       <c r="F97" s="12"/>
       <c r="G97" s="12"/>
@@ -3335,7 +3335,7 @@
       <c r="L97" s="12"/>
       <c r="M97" s="12"/>
     </row>
-    <row r="98" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C98" s="105" t="s">
         <v>101</v>
       </c>
@@ -3360,7 +3360,7 @@
       <c r="L98" s="12"/>
       <c r="M98" s="12"/>
     </row>
-    <row r="99" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C99" s="105" t="s">
         <v>102</v>
       </c>
@@ -3389,7 +3389,7 @@
       <c r="L99" s="145"/>
       <c r="M99" s="145"/>
     </row>
-    <row r="100" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C100" s="103" t="s">
         <v>111</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>6.0870447397788373E-2</v>
       </c>
       <c r="H100" s="72">
-        <f t="shared" ref="H100:M100" si="12">+H98/H$74</f>
+        <f t="shared" ref="H100" si="12">+H98/H$74</f>
         <v>6.8306010928961755E-2</v>
       </c>
       <c r="I100" s="72"/>
@@ -3418,7 +3418,7 @@
       <c r="L100" s="72"/>
       <c r="M100" s="72"/>
     </row>
-    <row r="101" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C101" s="26"/>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
@@ -3429,7 +3429,7 @@
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
     </row>
-    <row r="102" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C102" s="105" t="s">
         <v>103</v>
       </c>
@@ -3454,7 +3454,7 @@
       <c r="L102" s="12"/>
       <c r="M102" s="12"/>
     </row>
-    <row r="103" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C103" s="103" t="s">
         <v>104</v>
       </c>
@@ -3483,7 +3483,7 @@
       <c r="L103" s="113"/>
       <c r="M103" s="113"/>
     </row>
-    <row r="104" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C104" s="26"/>
       <c r="F104" s="12"/>
       <c r="G104" s="12"/>
@@ -3494,7 +3494,7 @@
       <c r="L104" s="12"/>
       <c r="M104" s="12"/>
     </row>
-    <row r="105" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C105" s="105" t="s">
         <v>105</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="L105" s="12"/>
       <c r="M105" s="12"/>
     </row>
-    <row r="106" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C106" s="103" t="s">
         <v>104</v>
       </c>
@@ -3548,7 +3548,7 @@
       <c r="L106" s="113"/>
       <c r="M106" s="113"/>
     </row>
-    <row r="107" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C107" s="26"/>
       <c r="F107" s="12"/>
       <c r="G107" s="12"/>
@@ -3559,7 +3559,7 @@
       <c r="L107" s="12"/>
       <c r="M107" s="12"/>
     </row>
-    <row r="108" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C108" s="105" t="s">
         <v>106</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="L108" s="12"/>
       <c r="M108" s="12"/>
     </row>
-    <row r="109" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C109" s="103" t="s">
         <v>104</v>
       </c>
@@ -3613,7 +3613,7 @@
       <c r="L109" s="113"/>
       <c r="M109" s="113"/>
     </row>
-    <row r="110" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C110" s="26"/>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
@@ -3624,7 +3624,7 @@
       <c r="L110" s="12"/>
       <c r="M110" s="12"/>
     </row>
-    <row r="111" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C111" s="105" t="s">
         <v>107</v>
       </c>
@@ -3649,7 +3649,7 @@
       <c r="L111" s="12"/>
       <c r="M111" s="12"/>
     </row>
-    <row r="112" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C112" s="103" t="s">
         <v>111</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="113" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C113" s="26"/>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
@@ -3699,7 +3699,7 @@
       <c r="L113" s="12"/>
       <c r="M113" s="12"/>
     </row>
-    <row r="114" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C114" s="105" t="s">
         <v>108</v>
       </c>
@@ -3724,7 +3724,7 @@
       <c r="L114" s="12"/>
       <c r="M114" s="12"/>
     </row>
-    <row r="115" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C115" s="103" t="s">
         <v>104</v>
       </c>
@@ -3753,7 +3753,7 @@
       <c r="L115" s="13"/>
       <c r="M115" s="13"/>
     </row>
-    <row r="116" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C116" s="26"/>
       <c r="F116" s="12"/>
       <c r="G116" s="12"/>
@@ -3764,7 +3764,7 @@
       <c r="L116" s="12"/>
       <c r="M116" s="12"/>
     </row>
-    <row r="117" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C117" s="105" t="s">
         <v>109</v>
       </c>
@@ -3793,7 +3793,7 @@
       <c r="L117" s="12"/>
       <c r="M117" s="12"/>
     </row>
-    <row r="118" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C118" s="105" t="s">
         <v>110</v>
       </c>
@@ -3821,7 +3821,7 @@
       <c r="L118" s="12"/>
       <c r="M118" s="12"/>
     </row>
-    <row r="119" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C119" s="105" t="s">
         <v>112</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>-0.11092525750506205</v>
       </c>
       <c r="F119" s="72">
-        <f t="shared" ref="F119:I119" si="17">+F118/(F74-E74)</f>
+        <f t="shared" ref="F119:H119" si="17">+F118/(F74-E74)</f>
         <v>-0.33704952035260544</v>
       </c>
       <c r="G119" s="72">
@@ -3850,7 +3850,7 @@
       <c r="L119" s="72"/>
       <c r="M119" s="72"/>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C120" s="26"/>
       <c r="F120" s="12"/>
       <c r="G120" s="12"/>
@@ -3861,7 +3861,7 @@
       <c r="L120" s="12"/>
       <c r="M120" s="12"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121" s="31"/>
       <c r="C121" s="32"/>
       <c r="D121" s="33"/>
@@ -3881,7 +3881,7 @@
       <c r="L121" s="21"/>
       <c r="M121" s="21"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="s">
         <v>32</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="123" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C123" s="4"/>
       <c r="F123" s="30"/>
       <c r="G123" s="30"/>
@@ -3938,7 +3938,7 @@
       <c r="L123" s="30"/>
       <c r="M123" s="30"/>
     </row>
-    <row r="124" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C124" s="4" t="s">
         <v>25</v>
       </c>
@@ -3967,7 +3967,7 @@
       <c r="L124" s="107"/>
       <c r="M124" s="107"/>
     </row>
-    <row r="125" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C125" s="11" t="s">
         <v>29</v>
       </c>
@@ -3992,7 +3992,7 @@
       <c r="L125" s="12"/>
       <c r="M125" s="12"/>
     </row>
-    <row r="126" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C126" s="11" t="s">
         <v>30</v>
       </c>
@@ -4021,7 +4021,7 @@
       <c r="L126" s="47"/>
       <c r="M126" s="47"/>
     </row>
-    <row r="127" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C127" s="103" t="s">
         <v>113</v>
       </c>
@@ -4050,7 +4050,7 @@
       <c r="L127" s="12"/>
       <c r="M127" s="12"/>
     </row>
-    <row r="128" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C128" s="103" t="s">
         <v>114</v>
       </c>
@@ -4079,7 +4079,7 @@
       <c r="L128" s="29"/>
       <c r="M128" s="29"/>
     </row>
-    <row r="129" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C129" s="43" t="s">
         <v>31</v>
       </c>
@@ -4108,7 +4108,7 @@
       <c r="L129" s="106"/>
       <c r="M129" s="106"/>
     </row>
-    <row r="130" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C130" s="4"/>
       <c r="F130" s="30"/>
       <c r="G130" s="30"/>
@@ -4119,7 +4119,7 @@
       <c r="L130" s="30"/>
       <c r="M130" s="30"/>
     </row>
-    <row r="131" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C131" s="3" t="s">
         <v>33</v>
       </c>
@@ -4136,7 +4136,7 @@
       <c r="L131" s="64"/>
       <c r="M131" s="64"/>
     </row>
-    <row r="132" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C132" s="57" t="s">
         <v>48</v>
       </c>
@@ -4153,7 +4153,7 @@
       <c r="L132" s="64"/>
       <c r="M132" s="64"/>
     </row>
-    <row r="133" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C133" s="57" t="s">
         <v>54</v>
       </c>
@@ -4170,7 +4170,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="12"/>
     </row>
-    <row r="134" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C134" s="43" t="s">
         <v>35</v>
       </c>
@@ -4190,7 +4190,7 @@
       <c r="L134" s="46"/>
       <c r="M134" s="46"/>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C135" s="4"/>
       <c r="I135" s="12"/>
       <c r="J135" s="12"/>
@@ -4198,7 +4198,7 @@
       <c r="L135" s="12"/>
       <c r="M135" s="12"/>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B136" s="31"/>
       <c r="C136" s="32"/>
       <c r="D136" s="33"/>
@@ -4218,7 +4218,7 @@
       <c r="L136" s="21"/>
       <c r="M136" s="21"/>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B137" s="5" t="s">
         <v>7</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="138" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B138" s="52"/>
       <c r="C138" s="53"/>
       <c r="D138" s="54"/>
@@ -4278,7 +4278,7 @@
       <c r="L138" s="55"/>
       <c r="M138" s="55"/>
     </row>
-    <row r="139" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B139" s="52"/>
       <c r="C139" s="9" t="s">
         <v>134</v>
@@ -4294,7 +4294,7 @@
       <c r="L139" s="9"/>
       <c r="M139" s="9"/>
     </row>
-    <row r="140" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B140" s="52"/>
       <c r="C140" s="129" t="s">
         <v>43</v>
@@ -4322,7 +4322,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B141" s="52"/>
       <c r="C141" s="129"/>
       <c r="D141" s="67"/>
@@ -4336,7 +4336,7 @@
       <c r="L141" s="61"/>
       <c r="M141" s="61"/>
     </row>
-    <row r="142" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B142" s="52"/>
       <c r="C142" s="11" t="str">
         <f>+$C$23</f>
@@ -4370,7 +4370,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="143" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B143" s="52"/>
       <c r="C143" s="11" t="str">
         <f>+$C$24</f>
@@ -4404,7 +4404,7 @@
         <v>8.199999999999999E-2</v>
       </c>
     </row>
-    <row r="144" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B144" s="52"/>
       <c r="C144" s="11" t="str">
         <f>+$C$25</f>
@@ -4438,7 +4438,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="145" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B145" s="52"/>
       <c r="C145" s="11" t="str">
         <f>+$C$26</f>
@@ -4472,7 +4472,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="146" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B146" s="52"/>
       <c r="C146" s="11" t="s">
         <v>121</v>
@@ -4505,7 +4505,7 @@
         <v>4.1999999999999996E-2</v>
       </c>
     </row>
-    <row r="147" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B147" s="52"/>
       <c r="C147" s="53"/>
       <c r="D147" s="54"/>
@@ -4519,7 +4519,7 @@
       <c r="L147" s="55"/>
       <c r="M147" s="55"/>
     </row>
-    <row r="148" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C148" s="9" t="s">
         <v>158</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="L148" s="9"/>
       <c r="M148" s="9"/>
     </row>
-    <row r="149" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C149" s="11" t="s">
         <v>33</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C150" s="58" t="s">
         <v>48</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C151" s="130" t="s">
         <v>139</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>-0.29804012539644065</v>
       </c>
     </row>
-    <row r="152" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C152" s="58" t="s">
         <v>53</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="153" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C153" s="59" t="s">
         <v>49</v>
       </c>
@@ -4682,10 +4682,10 @@
         <v>-50.29804012539644</v>
       </c>
     </row>
-    <row r="154" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C154" s="11"/>
     </row>
-    <row r="155" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C155" s="57" t="s">
         <v>50</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>151.19216050158576</v>
       </c>
     </row>
-    <row r="156" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C156" s="63" t="s">
         <v>51</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>50.29804012539644</v>
       </c>
     </row>
-    <row r="157" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C157" s="35" t="s">
         <v>52</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>201.49020062698219</v>
       </c>
     </row>
-    <row r="158" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C158" s="147" t="s">
         <v>140</v>
       </c>
@@ -4808,10 +4808,10 @@
         <v>10.885835556114175</v>
       </c>
     </row>
-    <row r="159" spans="2:13" ht="14.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:13" ht="14.55" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C159" s="11"/>
     </row>
-    <row r="160" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C160" s="9" t="s">
         <v>122</v>
       </c>
@@ -4826,7 +4826,7 @@
       <c r="L160" s="9"/>
       <c r="M160" s="9"/>
     </row>
-    <row r="161" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C161" s="103" t="s">
         <v>136</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>28.611852038058302</v>
       </c>
     </row>
-    <row r="162" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C162" s="130" t="s">
         <v>139</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>-0.29804012539644065</v>
       </c>
     </row>
-    <row r="163" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C163" s="59" t="s">
         <v>135</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>28.313811912661862</v>
       </c>
     </row>
-    <row r="164" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C164" s="147" t="s">
         <v>140</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>2.3461718671207805</v>
       </c>
     </row>
-    <row r="165" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C165" s="11"/>
       <c r="I165" s="62"/>
       <c r="J165" s="62"/>
@@ -4956,7 +4956,7 @@
       <c r="L165" s="62"/>
       <c r="M165" s="62"/>
     </row>
-    <row r="166" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C166" s="9" t="s">
         <v>123</v>
       </c>
@@ -4971,7 +4971,7 @@
       <c r="L166" s="9"/>
       <c r="M166" s="9"/>
     </row>
-    <row r="167" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C167" s="103" t="s">
         <v>137</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>100.6340360601596</v>
       </c>
     </row>
-    <row r="168" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C168" s="58" t="s">
         <v>46</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>3.0190210818047878</v>
       </c>
     </row>
-    <row r="169" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C169" s="59" t="s">
         <v>138</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>103.6530571419644</v>
       </c>
     </row>
-    <row r="170" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C170" s="147" t="s">
         <v>140</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>8.0507228848127674</v>
       </c>
     </row>
-    <row r="171" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C171" s="11"/>
       <c r="I171" s="12"/>
       <c r="J171" s="12"/>
@@ -5101,7 +5101,7 @@
       <c r="L171" s="12"/>
       <c r="M171" s="12"/>
     </row>
-    <row r="172" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C172" s="9" t="s">
         <v>20</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="L172" s="9"/>
       <c r="M172" s="9"/>
     </row>
-    <row r="173" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C173" s="57" t="s">
         <v>45</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>81.096060047774614</v>
       </c>
     </row>
-    <row r="174" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C174" s="58" t="s">
         <v>46</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>6.4876848038219697</v>
       </c>
     </row>
-    <row r="175" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C175" s="59" t="s">
         <v>44</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>87.583744851596578</v>
       </c>
     </row>
-    <row r="176" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C176" s="147" t="s">
         <v>140</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>3.2438424019109848</v>
       </c>
     </row>
-    <row r="177" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C177" s="11"/>
       <c r="I177" s="12"/>
       <c r="J177" s="12"/>
@@ -5246,7 +5246,7 @@
       <c r="L177" s="12"/>
       <c r="M177" s="12"/>
     </row>
-    <row r="178" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C178" s="9" t="s">
         <v>47</v>
       </c>
@@ -5261,7 +5261,7 @@
       <c r="L178" s="9"/>
       <c r="M178" s="9"/>
     </row>
-    <row r="179" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C179" s="57" t="s">
         <v>34</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C180" s="103" t="s">
         <v>140</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>-24.52657270995871</v>
       </c>
     </row>
-    <row r="181" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C181" s="103" t="s">
         <v>141</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>-34.033278595585465</v>
       </c>
     </row>
-    <row r="182" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C182" s="103" t="s">
         <v>157</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" s="31"/>
       <c r="C184" s="32"/>
       <c r="D184" s="33"/>
@@ -5397,7 +5397,7 @@
       <c r="L184" s="21"/>
       <c r="M184" s="21"/>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" s="5" t="s">
         <v>161</v>
       </c>
@@ -5443,10 +5443,10 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="186" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="H186" s="25"/>
     </row>
-    <row r="187" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C187" s="56" t="s">
         <v>8</v>
       </c>
@@ -5474,8 +5474,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="189" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C189" s="4" t="s">
         <v>25</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C190" s="57" t="s">
         <v>55</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C191" s="43" t="s">
         <v>57</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C192" s="68" t="s">
         <v>9</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>-421.04081453320504</v>
       </c>
     </row>
-    <row r="193" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C193" s="4" t="s">
         <v>56</v>
       </c>
@@ -5621,8 +5621,8 @@
         <v>-421.04081453320504</v>
       </c>
     </row>
-    <row r="194" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="195" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="195" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C195" s="9" t="s">
         <v>58</v>
       </c>
@@ -5637,7 +5637,7 @@
       <c r="L195" s="10"/>
       <c r="M195" s="10"/>
     </row>
-    <row r="196" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C196" s="57" t="s">
         <v>60</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>-0.66753938768893273</v>
       </c>
     </row>
-    <row r="197" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C197" s="57" t="s">
         <v>59</v>
       </c>
@@ -5695,8 +5695,8 @@
         <v>-1.9223492080517777</v>
       </c>
     </row>
-    <row r="198" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="199" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="199" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C199" s="9" t="s">
         <v>142</v>
       </c>
@@ -5711,7 +5711,7 @@
       <c r="L199" s="10"/>
       <c r="M199" s="10"/>
     </row>
-    <row r="200" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C200" s="103" t="s">
         <v>155</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C201" s="103" t="s">
         <v>156</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C202" s="147" t="s">
         <v>159</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C203" s="43" t="s">
         <v>160</v>
       </c>
@@ -5827,14 +5827,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="I204" s="71"/>
       <c r="J204" s="154"/>
       <c r="K204" s="154"/>
       <c r="L204" s="154"/>
       <c r="M204" s="154"/>
     </row>
-    <row r="205" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C205" s="4" t="s">
         <v>144</v>
       </c>
@@ -5862,8 +5862,8 @@
         <v>-421.04081453320504</v>
       </c>
     </row>
-    <row r="206" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="207" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="207" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C207" s="9" t="s">
         <v>162</v>
       </c>
@@ -5878,7 +5878,7 @@
       <c r="L207" s="10"/>
       <c r="M207" s="10"/>
     </row>
-    <row r="208" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C208" s="57" t="s">
         <v>60</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>-0.66753938768893273</v>
       </c>
     </row>
-    <row r="209" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C209" s="57" t="s">
         <v>59</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>-1.9223492080517777</v>
       </c>
     </row>
-    <row r="211" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B211" s="5" t="s">
         <v>163</v>
       </c>
@@ -5952,8 +5952,8 @@
       <c r="L211" s="6"/>
       <c r="M211" s="6"/>
     </row>
-    <row r="212" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="213" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="213" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C213" s="73"/>
       <c r="D213" s="74"/>
       <c r="E213" s="75" t="str">
@@ -5969,7 +5969,7 @@
       <c r="L213" s="76"/>
       <c r="M213" s="77"/>
     </row>
-    <row r="214" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C214" s="78"/>
       <c r="D214" s="79">
         <f>+$M$209</f>
@@ -6011,7 +6011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="215" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C215" s="156" t="s">
         <v>154</v>
       </c>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="N215" s="80"/>
     </row>
-    <row r="216" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C216" s="157"/>
       <c r="D216" s="140">
         <f>+D215-5%</f>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="N216" s="80"/>
     </row>
-    <row r="217" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C217" s="157"/>
       <c r="D217" s="140">
         <f t="shared" ref="D217:D223" si="60">+D216-5%</f>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="N217" s="80"/>
     </row>
-    <row r="218" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C218" s="157"/>
       <c r="D218" s="140">
         <f t="shared" si="60"/>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="N218" s="80"/>
     </row>
-    <row r="219" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C219" s="157"/>
       <c r="D219" s="142">
         <f t="shared" si="60"/>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="N219" s="81"/>
     </row>
-    <row r="220" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C220" s="157"/>
       <c r="D220" s="140">
         <f t="shared" si="60"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="N220" s="80"/>
     </row>
-    <row r="221" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C221" s="157"/>
       <c r="D221" s="140">
         <f t="shared" si="60"/>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="N221" s="80"/>
     </row>
-    <row r="222" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C222" s="157"/>
       <c r="D222" s="140">
         <f t="shared" si="60"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="N222" s="80"/>
     </row>
-    <row r="223" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C223" s="158"/>
       <c r="D223" s="141">
         <f t="shared" si="60"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="N223" s="80"/>
     </row>
-    <row r="225" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B225" s="31"/>
       <c r="C225" s="32"/>
       <c r="D225" s="33"/>
@@ -6348,7 +6348,7 @@
       <c r="L225" s="21"/>
       <c r="M225" s="21"/>
     </row>
-    <row r="226" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B226" s="5" t="s">
         <v>63</v>
       </c>
@@ -6394,8 +6394,8 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="227" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="228" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="228" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C228" s="9" t="s">
         <v>152</v>
       </c>
@@ -6410,7 +6410,7 @@
       <c r="L228" s="10"/>
       <c r="M228" s="10"/>
     </row>
-    <row r="229" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C229" s="84" t="s">
         <v>64</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>-737.38011279300008</v>
       </c>
     </row>
-    <row r="230" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C230" s="84" t="s">
         <v>65</v>
       </c>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="N230" s="12"/>
     </row>
-    <row r="231" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C231" s="85" t="s">
         <v>66</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>-314.39623929534059</v>
       </c>
     </row>
-    <row r="232" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C232" s="4" t="s">
         <v>67</v>
       </c>
@@ -6530,8 +6530,8 @@
         <v>-1051.7763520883407</v>
       </c>
     </row>
-    <row r="233" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="234" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="234" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C234" s="9" t="s">
         <v>68</v>
       </c>
@@ -6546,7 +6546,7 @@
       <c r="L234" s="10"/>
       <c r="M234" s="10"/>
     </row>
-    <row r="235" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C235" s="84" t="str">
         <f>+$C$229</f>
         <v>EBITDA Growth:</v>
@@ -6576,7 +6576,7 @@
         <v>0.70108071105506864</v>
       </c>
     </row>
-    <row r="236" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C236" s="84" t="str">
         <f>+$C$230</f>
         <v>Multiple Expansion:</v>
@@ -6606,7 +6606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C237" s="85" t="str">
         <f>+$C$231</f>
         <v>Debt Paydown and Cash Generation:</v>
@@ -6639,7 +6639,7 @@
         <v>0.29891928894493136</v>
       </c>
     </row>
-    <row r="238" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C238" s="4" t="str">
         <f>+$C$232</f>
         <v>Total Equity Return:</v>
@@ -6669,8 +6669,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="240" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="240" spans="2:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C240" s="9" t="s">
         <v>148</v>
       </c>
@@ -6685,7 +6685,7 @@
       <c r="L240" s="10"/>
       <c r="M240" s="10"/>
     </row>
-    <row r="241" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C241" s="103" t="s">
         <v>150</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>-150.22252893374997</v>
       </c>
     </row>
-    <row r="242" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C242" s="126" t="s">
         <v>151</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C243" s="4" t="s">
         <v>149</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>-150.22252893374997</v>
       </c>
     </row>
-    <row r="244" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="I244" s="12"/>
       <c r="J244" s="12"/>
       <c r="K244" s="12"/>
@@ -6783,7 +6783,7 @@
       <c r="M244" s="12"/>
       <c r="N244" s="12"/>
     </row>
-    <row r="245" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C245" s="9" t="s">
         <v>153</v>
       </c>
@@ -6798,7 +6798,7 @@
       <c r="L245" s="10"/>
       <c r="M245" s="10"/>
     </row>
-    <row r="246" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C246" s="84" t="str">
         <f>+$C$241</f>
         <v>Volume Growth:</v>
@@ -6828,7 +6828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C247" s="85" t="str">
         <f>+$C$242</f>
         <v>TCE Rate Growth:</v>
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C248" s="4" t="str">
         <f>+$C$243</f>
         <v>TCE Revenue Growth:</v>
